--- a/src/excel-data/kanto.xlsx
+++ b/src/excel-data/kanto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/Cao Yuxuan/テストweb/findmyrailpass.net/src/excel-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BC7765-38A8-434B-937C-7B4A8FADC3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB33D9AF-FE21-894E-99E2-13AA4F753314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="960" windowWidth="32680" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="736">
   <si>
     <t>sortOrder</t>
   </si>
@@ -2540,22 +2540,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>※急行需要加钱</t>
-    <rPh sb="1" eb="2">
-      <t>ji xing</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>xing</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>xu yao</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>jia q</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>埼玉; 秩父; 关东</t>
     <rPh sb="0" eb="2">
       <t>サイタマ</t>
@@ -4474,6 +4458,26 @@
   </si>
   <si>
     <t>/images/coverage/NIKKO-PASS-world-heritage-area.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※坐普通电车以外需另外加钱</t>
+    <rPh sb="1" eb="2">
+      <t>ji xing</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>xing</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>xu yao</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>jia q</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※指定席需要预约，一等座需要加钱</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4649,7 +4653,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4675,7 +4679,6 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -5137,6 +5140,9 @@
       </c>
     </row>
     <row r="2" spans="1:30" s="5" customFormat="1">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
       <c r="B2" s="6" t="s">
         <v>27</v>
       </c>
@@ -5211,6 +5217,9 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="5" customFormat="1" ht="32">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
       <c r="B3" s="6" t="s">
         <v>29</v>
       </c>
@@ -5242,7 +5251,7 @@
         <v>25</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="W3" s="7" t="s">
         <v>358</v>
@@ -5257,13 +5266,16 @@
         <v>4</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AD3" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:30" s="5" customFormat="1" ht="32">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
       <c r="B4" s="6" t="s">
         <v>31</v>
       </c>
@@ -5295,7 +5307,7 @@
         <v>25</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="W4" s="7" t="s">
         <v>359</v>
@@ -5310,13 +5322,16 @@
         <v>4</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AD4" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:30" s="5" customFormat="1" ht="48">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
       <c r="B5" s="6" t="s">
         <v>33</v>
       </c>
@@ -5348,7 +5363,7 @@
         <v>25</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="W5" s="7" t="s">
         <v>360</v>
@@ -5366,13 +5381,16 @@
         <v>1</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AD5" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:30" s="5" customFormat="1">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
       <c r="B6" s="6" t="s">
         <v>35</v>
       </c>
@@ -5404,7 +5422,7 @@
         <v>25</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>362</v>
@@ -5419,13 +5437,16 @@
         <v>3</v>
       </c>
       <c r="AB6" s="5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AD6" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:30" s="5" customFormat="1" ht="48">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
       <c r="B7" s="6" t="s">
         <v>37</v>
       </c>
@@ -5457,7 +5478,7 @@
         <v>25</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="W7" s="7" t="s">
         <v>363</v>
@@ -5472,13 +5493,16 @@
         <v>3</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AD7" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:30" s="5" customFormat="1" ht="32">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
       <c r="B8" s="6" t="s">
         <v>39</v>
       </c>
@@ -5510,7 +5534,7 @@
         <v>25</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="W8" s="7" t="s">
         <v>366</v>
@@ -5525,13 +5549,16 @@
         <v>3</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AD8" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:30" s="5" customFormat="1" ht="409.6">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
       <c r="B9" s="6" t="s">
         <v>41</v>
       </c>
@@ -5579,6 +5606,9 @@
       </c>
     </row>
     <row r="10" spans="1:30" s="5" customFormat="1">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
       <c r="B10" s="6" t="s">
         <v>43</v>
       </c>
@@ -5629,6 +5659,9 @@
       </c>
     </row>
     <row r="11" spans="1:30" s="5" customFormat="1">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
       <c r="B11" s="6" t="s">
         <v>45</v>
       </c>
@@ -5679,6 +5712,9 @@
       </c>
     </row>
     <row r="12" spans="1:30" s="5" customFormat="1" ht="32">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
       <c r="B12" s="6" t="s">
         <v>47</v>
       </c>
@@ -5729,6 +5765,9 @@
       </c>
     </row>
     <row r="13" spans="1:30" s="5" customFormat="1" ht="80">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
       <c r="B13" s="6" t="s">
         <v>50</v>
       </c>
@@ -5775,13 +5814,16 @@
         <v>1</v>
       </c>
       <c r="AB13" s="8" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AD13" s="6" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:30" s="5" customFormat="1" ht="32">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
       <c r="B14" s="6" t="s">
         <v>51</v>
       </c>
@@ -5832,6 +5874,9 @@
       </c>
     </row>
     <row r="15" spans="1:30" s="5" customFormat="1">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
       <c r="B15" s="6" t="s">
         <v>52</v>
       </c>
@@ -5885,6 +5930,9 @@
       </c>
     </row>
     <row r="16" spans="1:30" s="5" customFormat="1" ht="16">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
       <c r="B16" s="6" t="s">
         <v>53</v>
       </c>
@@ -5937,7 +5985,10 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:30" s="5" customFormat="1">
+    <row r="17" spans="1:30" s="5" customFormat="1">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
       <c r="B17" s="6" t="s">
         <v>55</v>
       </c>
@@ -5990,7 +6041,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="2:30" s="5" customFormat="1">
+    <row r="18" spans="1:30" s="5" customFormat="1">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
       <c r="B18" s="6" t="s">
         <v>57</v>
       </c>
@@ -6040,7 +6094,10 @@
         <v>303</v>
       </c>
     </row>
-    <row r="19" spans="2:30" s="5" customFormat="1" ht="64">
+    <row r="19" spans="1:30" s="5" customFormat="1" ht="64">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
       <c r="B19" s="6" t="s">
         <v>58</v>
       </c>
@@ -6096,7 +6153,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="2:30" s="5" customFormat="1">
+    <row r="20" spans="1:30" s="5" customFormat="1">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
       <c r="B20" s="6" t="s">
         <v>60</v>
       </c>
@@ -6146,7 +6206,10 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="2:30" s="5" customFormat="1" ht="32">
+    <row r="21" spans="1:30" s="5" customFormat="1" ht="32">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
       <c r="B21" s="6" t="s">
         <v>62</v>
       </c>
@@ -6196,13 +6259,16 @@
         <v>1</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AD21" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="2:30" s="5" customFormat="1">
+    <row r="22" spans="1:30" s="5" customFormat="1">
+      <c r="A22" s="5">
+        <v>21</v>
+      </c>
       <c r="B22" s="6" t="s">
         <v>64</v>
       </c>
@@ -6252,7 +6318,10 @@
         <v>288</v>
       </c>
     </row>
-    <row r="23" spans="2:30" s="5" customFormat="1">
+    <row r="23" spans="1:30" s="5" customFormat="1">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
       <c r="B23" s="6" t="s">
         <v>65</v>
       </c>
@@ -6302,7 +6371,10 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:30" s="5" customFormat="1">
+    <row r="24" spans="1:30" s="5" customFormat="1">
+      <c r="A24" s="5">
+        <v>23</v>
+      </c>
       <c r="B24" s="6" t="s">
         <v>67</v>
       </c>
@@ -6352,7 +6424,10 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="2:30" s="5" customFormat="1">
+    <row r="25" spans="1:30" s="5" customFormat="1">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
       <c r="B25" s="6" t="s">
         <v>69</v>
       </c>
@@ -6402,7 +6477,10 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:30" s="5" customFormat="1">
+    <row r="26" spans="1:30" s="5" customFormat="1">
+      <c r="A26" s="5">
+        <v>25</v>
+      </c>
       <c r="B26" s="6" t="s">
         <v>71</v>
       </c>
@@ -6452,7 +6530,10 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="2:30" s="5" customFormat="1">
+    <row r="27" spans="1:30" s="5" customFormat="1">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
       <c r="B27" s="6" t="s">
         <v>165</v>
       </c>
@@ -6505,7 +6586,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="28" spans="2:30" s="5" customFormat="1">
+    <row r="28" spans="1:30" s="5" customFormat="1">
+      <c r="A28" s="5">
+        <v>27</v>
+      </c>
       <c r="B28" s="6" t="s">
         <v>438</v>
       </c>
@@ -6558,7 +6642,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="29" spans="2:30" s="5" customFormat="1">
+    <row r="29" spans="1:30" s="5" customFormat="1">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
       <c r="B29" s="6" t="s">
         <v>441</v>
       </c>
@@ -6611,7 +6698,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="30" spans="2:30" s="5" customFormat="1">
+    <row r="30" spans="1:30" s="5" customFormat="1">
+      <c r="A30" s="5">
+        <v>29</v>
+      </c>
       <c r="B30" s="6" t="s">
         <v>168</v>
       </c>
@@ -6661,7 +6751,10 @@
         <v>169</v>
       </c>
     </row>
-    <row r="31" spans="2:30" s="5" customFormat="1">
+    <row r="31" spans="1:30" s="5" customFormat="1">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
       <c r="B31" s="6" t="s">
         <v>171</v>
       </c>
@@ -6714,7 +6807,10 @@
         <v>172</v>
       </c>
     </row>
-    <row r="32" spans="2:30" s="5" customFormat="1">
+    <row r="32" spans="1:30" s="5" customFormat="1">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
       <c r="B32" s="6" t="s">
         <v>174</v>
       </c>
@@ -6764,7 +6860,10 @@
         <v>175</v>
       </c>
     </row>
-    <row r="33" spans="2:30" s="5" customFormat="1">
+    <row r="33" spans="1:30" s="5" customFormat="1">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
       <c r="B33" s="6" t="s">
         <v>177</v>
       </c>
@@ -6814,7 +6913,10 @@
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="2:30" s="5" customFormat="1">
+    <row r="34" spans="1:30" s="5" customFormat="1">
+      <c r="A34" s="5">
+        <v>33</v>
+      </c>
       <c r="B34" s="6" t="s">
         <v>180</v>
       </c>
@@ -6864,7 +6966,10 @@
         <v>181</v>
       </c>
     </row>
-    <row r="35" spans="2:30" s="5" customFormat="1" ht="16">
+    <row r="35" spans="1:30" s="5" customFormat="1" ht="16">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
       <c r="B35" s="6" t="s">
         <v>183</v>
       </c>
@@ -6917,7 +7022,10 @@
         <v>290</v>
       </c>
     </row>
-    <row r="36" spans="2:30" s="5" customFormat="1" ht="16">
+    <row r="36" spans="1:30" s="5" customFormat="1" ht="16">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
       <c r="B36" s="6" t="s">
         <v>185</v>
       </c>
@@ -6970,7 +7078,10 @@
         <v>291</v>
       </c>
     </row>
-    <row r="37" spans="2:30" s="5" customFormat="1">
+    <row r="37" spans="1:30" s="5" customFormat="1">
+      <c r="A37" s="5">
+        <v>36</v>
+      </c>
       <c r="B37" s="6" t="s">
         <v>187</v>
       </c>
@@ -7020,7 +7131,10 @@
         <v>188</v>
       </c>
     </row>
-    <row r="38" spans="2:30" s="5" customFormat="1">
+    <row r="38" spans="1:30" s="5" customFormat="1">
+      <c r="A38" s="5">
+        <v>37</v>
+      </c>
       <c r="B38" s="6" t="s">
         <v>190</v>
       </c>
@@ -7070,7 +7184,10 @@
         <v>191</v>
       </c>
     </row>
-    <row r="39" spans="2:30" s="5" customFormat="1">
+    <row r="39" spans="1:30" s="5" customFormat="1">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
       <c r="B39" s="6" t="s">
         <v>193</v>
       </c>
@@ -7120,7 +7237,10 @@
         <v>194</v>
       </c>
     </row>
-    <row r="40" spans="2:30" s="5" customFormat="1" ht="16">
+    <row r="40" spans="1:30" s="5" customFormat="1" ht="16">
+      <c r="A40" s="5">
+        <v>39</v>
+      </c>
       <c r="B40" s="6" t="s">
         <v>196</v>
       </c>
@@ -7170,7 +7290,10 @@
         <v>197</v>
       </c>
     </row>
-    <row r="41" spans="2:30" s="5" customFormat="1">
+    <row r="41" spans="1:30" s="5" customFormat="1">
+      <c r="A41" s="5">
+        <v>40</v>
+      </c>
       <c r="B41" s="6" t="s">
         <v>137</v>
       </c>
@@ -7202,7 +7325,7 @@
         <v>25</v>
       </c>
       <c r="V41" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="W41" s="7" t="s">
         <v>474</v>
@@ -7220,7 +7343,10 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="2:30" s="5" customFormat="1">
+    <row r="42" spans="1:30" s="5" customFormat="1">
+      <c r="A42" s="5">
+        <v>41</v>
+      </c>
       <c r="B42" s="6" t="s">
         <v>139</v>
       </c>
@@ -7252,7 +7378,7 @@
         <v>25</v>
       </c>
       <c r="V42" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="W42" s="7" t="s">
         <v>474</v>
@@ -7270,7 +7396,10 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="2:30" s="5" customFormat="1">
+    <row r="43" spans="1:30" s="5" customFormat="1">
+      <c r="A43" s="5">
+        <v>42</v>
+      </c>
       <c r="B43" s="6" t="s">
         <v>141</v>
       </c>
@@ -7320,7 +7449,10 @@
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="2:30" s="5" customFormat="1">
+    <row r="44" spans="1:30" s="5" customFormat="1">
+      <c r="A44" s="5">
+        <v>43</v>
+      </c>
       <c r="B44" s="6" t="s">
         <v>79</v>
       </c>
@@ -7343,7 +7475,7 @@
         <v>23</v>
       </c>
       <c r="S44" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T44" s="6" t="s">
         <v>202</v>
@@ -7364,13 +7496,16 @@
         <v>3</v>
       </c>
       <c r="AB44" s="5" t="s">
-        <v>481</v>
+        <v>734</v>
       </c>
       <c r="AD44" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="2:30" s="5" customFormat="1">
+    <row r="45" spans="1:30" s="5" customFormat="1">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
       <c r="B45" s="6" t="s">
         <v>203</v>
       </c>
@@ -7393,7 +7528,7 @@
         <v>23</v>
       </c>
       <c r="S45" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T45" s="6" t="s">
         <v>205</v>
@@ -7417,13 +7552,16 @@
         <v>4</v>
       </c>
       <c r="AB45" s="5" t="s">
-        <v>481</v>
+        <v>734</v>
       </c>
       <c r="AD45" s="6" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="46" spans="2:30" s="5" customFormat="1">
+    <row r="46" spans="1:30" s="5" customFormat="1">
+      <c r="A46" s="5">
+        <v>45</v>
+      </c>
       <c r="B46" s="6" t="s">
         <v>143</v>
       </c>
@@ -7446,7 +7584,7 @@
         <v>23</v>
       </c>
       <c r="S46" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T46" s="6" t="s">
         <v>206</v>
@@ -7458,7 +7596,7 @@
         <v>354</v>
       </c>
       <c r="W46" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="Y46" s="4" t="s">
         <v>361</v>
@@ -7470,7 +7608,10 @@
         <v>292</v>
       </c>
     </row>
-    <row r="47" spans="2:30" s="5" customFormat="1">
+    <row r="47" spans="1:30" s="5" customFormat="1">
+      <c r="A47" s="5">
+        <v>46</v>
+      </c>
       <c r="B47" s="6" t="s">
         <v>144</v>
       </c>
@@ -7493,7 +7634,7 @@
         <v>23</v>
       </c>
       <c r="S47" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="T47" s="6" t="s">
         <v>207</v>
@@ -7505,7 +7646,7 @@
         <v>354</v>
       </c>
       <c r="W47" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y47" s="4" t="s">
         <v>431</v>
@@ -7517,7 +7658,10 @@
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="2:30" s="5" customFormat="1">
+    <row r="48" spans="1:30" s="5" customFormat="1">
+      <c r="A48" s="5">
+        <v>47</v>
+      </c>
       <c r="B48" s="6" t="s">
         <v>73</v>
       </c>
@@ -7540,7 +7684,7 @@
         <v>23</v>
       </c>
       <c r="S48" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="T48" s="6" t="s">
         <v>233</v>
@@ -7552,7 +7696,7 @@
         <v>354</v>
       </c>
       <c r="W48" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X48" s="7"/>
       <c r="Y48" s="4" t="s">
@@ -7565,7 +7709,10 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="2:30" s="5" customFormat="1">
+    <row r="49" spans="1:30" s="5" customFormat="1">
+      <c r="A49" s="5">
+        <v>48</v>
+      </c>
       <c r="B49" s="6" t="s">
         <v>75</v>
       </c>
@@ -7576,7 +7723,7 @@
         <v>500</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="O49" s="5">
         <v>1</v>
@@ -7585,7 +7732,7 @@
         <v>23</v>
       </c>
       <c r="S49" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="T49" s="6" t="s">
         <v>234</v>
@@ -7597,7 +7744,7 @@
         <v>354</v>
       </c>
       <c r="W49" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Y49" s="4" t="s">
         <v>361</v>
@@ -7609,7 +7756,10 @@
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="2:30" s="5" customFormat="1">
+    <row r="50" spans="1:30" s="5" customFormat="1">
+      <c r="A50" s="5">
+        <v>49</v>
+      </c>
       <c r="B50" s="6" t="s">
         <v>75</v>
       </c>
@@ -7620,7 +7770,7 @@
         <v>700</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O50" s="5">
         <v>1</v>
@@ -7629,7 +7779,7 @@
         <v>23</v>
       </c>
       <c r="S50" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="T50" s="6" t="s">
         <v>234</v>
@@ -7641,7 +7791,7 @@
         <v>354</v>
       </c>
       <c r="W50" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Y50" s="4" t="s">
         <v>361</v>
@@ -7653,7 +7803,10 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="2:30" s="5" customFormat="1" ht="21" customHeight="1">
+    <row r="51" spans="1:30" s="5" customFormat="1" ht="21" customHeight="1">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
       <c r="B51" s="6" t="s">
         <v>77</v>
       </c>
@@ -7688,7 +7841,7 @@
         <v>354</v>
       </c>
       <c r="W51" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Y51" s="4" t="s">
         <v>361</v>
@@ -7697,18 +7850,21 @@
         <v>3</v>
       </c>
       <c r="AB51" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AD51" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="52" spans="2:30" s="5" customFormat="1">
+    <row r="52" spans="1:30" s="5" customFormat="1">
+      <c r="A52" s="5">
+        <v>51</v>
+      </c>
       <c r="B52" s="6" t="s">
         <v>81</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E52" s="10">
         <v>4860</v>
@@ -7717,7 +7873,7 @@
         <v>2410</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O52" s="5">
         <v>2</v>
@@ -7738,7 +7894,7 @@
         <v>354</v>
       </c>
       <c r="W52" s="7" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Y52" s="4" t="s">
         <v>361</v>
@@ -7750,7 +7906,10 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" spans="2:30" s="5" customFormat="1">
+    <row r="53" spans="1:30" s="5" customFormat="1">
+      <c r="A53" s="5">
+        <v>52</v>
+      </c>
       <c r="B53" s="6" t="s">
         <v>83</v>
       </c>
@@ -7764,7 +7923,7 @@
         <v>350</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O53" s="5">
         <v>1</v>
@@ -7773,7 +7932,7 @@
         <v>23</v>
       </c>
       <c r="S53" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="T53" s="6" t="s">
         <v>237</v>
@@ -7782,10 +7941,10 @@
         <v>25</v>
       </c>
       <c r="V53" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="W53" s="7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Y53" s="4" t="s">
         <v>431</v>
@@ -7797,7 +7956,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="2:30" s="5" customFormat="1">
+    <row r="54" spans="1:30" s="5" customFormat="1">
+      <c r="A54" s="5">
+        <v>53</v>
+      </c>
       <c r="B54" s="6" t="s">
         <v>86</v>
       </c>
@@ -7820,7 +7982,7 @@
         <v>23</v>
       </c>
       <c r="S54" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="T54" s="6" t="s">
         <v>238</v>
@@ -7829,10 +7991,10 @@
         <v>25</v>
       </c>
       <c r="V54" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="W54" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Y54" s="4" t="s">
         <v>431</v>
@@ -7844,12 +8006,15 @@
         <v>293</v>
       </c>
     </row>
-    <row r="55" spans="2:30" s="5" customFormat="1">
+    <row r="55" spans="1:30" s="5" customFormat="1">
+      <c r="A55" s="5">
+        <v>54</v>
+      </c>
       <c r="B55" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E55" s="10">
         <v>1600</v>
@@ -7867,16 +8032,16 @@
         <v>23</v>
       </c>
       <c r="S55" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="T55" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="U55" s="5" t="s">
         <v>25</v>
       </c>
       <c r="V55" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="W55" s="7" t="s">
         <v>358</v>
@@ -7889,12 +8054,15 @@
       </c>
       <c r="AD55" s="6"/>
     </row>
-    <row r="56" spans="2:30" s="5" customFormat="1">
+    <row r="56" spans="1:30" s="5" customFormat="1">
+      <c r="A56" s="5">
+        <v>55</v>
+      </c>
       <c r="B56" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E56" s="5">
         <v>700</v>
@@ -7912,7 +8080,7 @@
         <v>23</v>
       </c>
       <c r="S56" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="T56" s="6" t="s">
         <v>239</v>
@@ -7921,10 +8089,10 @@
         <v>25</v>
       </c>
       <c r="V56" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="W56" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="Y56" s="4" t="s">
         <v>431</v>
@@ -7936,7 +8104,10 @@
         <v>88</v>
       </c>
     </row>
-    <row r="57" spans="2:30" s="5" customFormat="1">
+    <row r="57" spans="1:30" s="5" customFormat="1">
+      <c r="A57" s="5">
+        <v>56</v>
+      </c>
       <c r="B57" s="6" t="s">
         <v>89</v>
       </c>
@@ -7959,7 +8130,7 @@
         <v>23</v>
       </c>
       <c r="S57" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="T57" s="6" t="s">
         <v>240</v>
@@ -7971,10 +8142,10 @@
         <v>354</v>
       </c>
       <c r="W57" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="X57" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Y57" s="4" t="s">
         <v>431</v>
@@ -7986,7 +8157,10 @@
         <v>294</v>
       </c>
     </row>
-    <row r="58" spans="2:30" s="5" customFormat="1">
+    <row r="58" spans="1:30" s="5" customFormat="1">
+      <c r="A58" s="5">
+        <v>57</v>
+      </c>
       <c r="B58" s="6" t="s">
         <v>90</v>
       </c>
@@ -8012,7 +8186,7 @@
         <v>23</v>
       </c>
       <c r="S58" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="T58" s="6" t="s">
         <v>241</v>
@@ -8024,10 +8198,10 @@
         <v>354</v>
       </c>
       <c r="W58" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="X58" s="7" t="s">
         <v>510</v>
-      </c>
-      <c r="X58" s="7" t="s">
-        <v>511</v>
       </c>
       <c r="Y58" s="4" t="s">
         <v>431</v>
@@ -8039,12 +8213,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="2:30" s="5" customFormat="1">
+    <row r="59" spans="1:30" s="5" customFormat="1">
+      <c r="A59" s="5">
+        <v>58</v>
+      </c>
       <c r="B59" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E59" s="10">
         <v>470</v>
@@ -8065,7 +8242,7 @@
         <v>23</v>
       </c>
       <c r="S59" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="T59" s="6" t="s">
         <v>242</v>
@@ -8077,10 +8254,10 @@
         <v>354</v>
       </c>
       <c r="W59" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="X59" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y59" s="4" t="s">
         <v>431</v>
@@ -8092,7 +8269,10 @@
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="2:30" s="5" customFormat="1">
+    <row r="60" spans="1:30" s="5" customFormat="1">
+      <c r="A60" s="5">
+        <v>59</v>
+      </c>
       <c r="B60" s="6" t="s">
         <v>94</v>
       </c>
@@ -8127,10 +8307,10 @@
         <v>354</v>
       </c>
       <c r="W60" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="X60" s="7" t="s">
         <v>518</v>
-      </c>
-      <c r="X60" s="7" t="s">
-        <v>519</v>
       </c>
       <c r="Y60" s="4" t="s">
         <v>431</v>
@@ -8139,13 +8319,16 @@
         <v>3</v>
       </c>
       <c r="AB60" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AD60" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="2:30" s="5" customFormat="1">
+    <row r="61" spans="1:30" s="5" customFormat="1">
+      <c r="A61" s="5">
+        <v>60</v>
+      </c>
       <c r="B61" s="6" t="s">
         <v>96</v>
       </c>
@@ -8171,7 +8354,7 @@
         <v>23</v>
       </c>
       <c r="S61" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T61" s="6" t="s">
         <v>244</v>
@@ -8183,10 +8366,10 @@
         <v>354</v>
       </c>
       <c r="W61" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="X61" s="7" t="s">
         <v>521</v>
-      </c>
-      <c r="X61" s="7" t="s">
-        <v>522</v>
       </c>
       <c r="Y61" s="4" t="s">
         <v>361</v>
@@ -8198,7 +8381,10 @@
         <v>97</v>
       </c>
     </row>
-    <row r="62" spans="2:30" s="5" customFormat="1">
+    <row r="62" spans="1:30" s="5" customFormat="1">
+      <c r="A62" s="5">
+        <v>61</v>
+      </c>
       <c r="B62" s="6" t="s">
         <v>98</v>
       </c>
@@ -8224,7 +8410,7 @@
         <v>23</v>
       </c>
       <c r="S62" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T62" s="6" t="s">
         <v>245</v>
@@ -8236,10 +8422,10 @@
         <v>354</v>
       </c>
       <c r="W62" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="X62" s="7" t="s">
         <v>524</v>
-      </c>
-      <c r="X62" s="7" t="s">
-        <v>525</v>
       </c>
       <c r="Y62" s="4" t="s">
         <v>361</v>
@@ -8248,13 +8434,16 @@
         <v>3</v>
       </c>
       <c r="AB62" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AD62" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="2:30" s="5" customFormat="1">
+    <row r="63" spans="1:30" s="5" customFormat="1">
+      <c r="A63" s="5">
+        <v>62</v>
+      </c>
       <c r="B63" s="6" t="s">
         <v>99</v>
       </c>
@@ -8271,7 +8460,7 @@
         <v>610</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="O63" s="5">
         <v>1</v>
@@ -8280,7 +8469,7 @@
         <v>23</v>
       </c>
       <c r="S63" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T63" s="6" t="s">
         <v>246</v>
@@ -8292,10 +8481,10 @@
         <v>354</v>
       </c>
       <c r="W63" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="X63" s="7" t="s">
         <v>527</v>
-      </c>
-      <c r="X63" s="7" t="s">
-        <v>528</v>
       </c>
       <c r="Y63" s="4" t="s">
         <v>361</v>
@@ -8304,13 +8493,16 @@
         <v>3</v>
       </c>
       <c r="AB63" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AD63" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="2:30" s="5" customFormat="1">
+    <row r="64" spans="1:30" s="5" customFormat="1">
+      <c r="A64" s="5">
+        <v>63</v>
+      </c>
       <c r="B64" s="6" t="s">
         <v>278</v>
       </c>
@@ -8321,7 +8513,7 @@
         <v>440</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="O64" s="5">
         <v>1</v>
@@ -8330,7 +8522,7 @@
         <v>23</v>
       </c>
       <c r="S64" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="T64" s="6" t="s">
         <v>279</v>
@@ -8342,10 +8534,10 @@
         <v>354</v>
       </c>
       <c r="W64" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="X64" s="7" t="s">
         <v>531</v>
-      </c>
-      <c r="X64" s="7" t="s">
-        <v>532</v>
       </c>
       <c r="Y64" s="4" t="s">
         <v>361</v>
@@ -8357,7 +8549,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="65" spans="2:30" s="5" customFormat="1">
+    <row r="65" spans="1:30" s="5" customFormat="1">
+      <c r="A65" s="5">
+        <v>64</v>
+      </c>
       <c r="B65" s="6" t="s">
         <v>146</v>
       </c>
@@ -8372,7 +8567,7 @@
         <v>520</v>
       </c>
       <c r="N65" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="O65" s="5">
         <v>1</v>
@@ -8381,7 +8576,7 @@
         <v>23</v>
       </c>
       <c r="S65" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="T65" s="6" t="s">
         <v>280</v>
@@ -8393,7 +8588,7 @@
         <v>354</v>
       </c>
       <c r="W65" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="Y65" s="4" t="s">
         <v>361</v>
@@ -8402,13 +8597,16 @@
         <v>3</v>
       </c>
       <c r="AB65" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AD65" s="6" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="66" spans="2:30" s="5" customFormat="1">
+    <row r="66" spans="1:30" s="5" customFormat="1">
+      <c r="A66" s="5">
+        <v>65</v>
+      </c>
       <c r="B66" s="6" t="s">
         <v>101</v>
       </c>
@@ -8422,7 +8620,7 @@
         <v>690</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="O66" s="5">
         <v>1</v>
@@ -8431,7 +8629,7 @@
         <v>23</v>
       </c>
       <c r="S66" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T66" s="6" t="s">
         <v>247</v>
@@ -8443,7 +8641,7 @@
         <v>354</v>
       </c>
       <c r="W66" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Y66" s="4" t="s">
         <v>361</v>
@@ -8452,13 +8650,16 @@
         <v>3</v>
       </c>
       <c r="AB66" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AD66" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="67" spans="2:30" s="5" customFormat="1">
+    <row r="67" spans="1:30" s="5" customFormat="1">
+      <c r="A67" s="5">
+        <v>66</v>
+      </c>
       <c r="B67" s="6" t="s">
         <v>103</v>
       </c>
@@ -8472,7 +8673,7 @@
         <v>840</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="O67" s="5">
         <v>1</v>
@@ -8481,7 +8682,7 @@
         <v>23</v>
       </c>
       <c r="S67" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T67" s="6" t="s">
         <v>248</v>
@@ -8493,7 +8694,7 @@
         <v>354</v>
       </c>
       <c r="W67" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Y67" s="4" t="s">
         <v>361</v>
@@ -8502,13 +8703,16 @@
         <v>3</v>
       </c>
       <c r="AB67" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AD67" s="6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="68" spans="2:30" s="5" customFormat="1">
+    <row r="68" spans="1:30" s="5" customFormat="1">
+      <c r="A68" s="5">
+        <v>67</v>
+      </c>
       <c r="B68" s="6" t="s">
         <v>105</v>
       </c>
@@ -8531,7 +8735,7 @@
         <v>23</v>
       </c>
       <c r="S68" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T68" s="6" t="s">
         <v>249</v>
@@ -8543,7 +8747,7 @@
         <v>354</v>
       </c>
       <c r="W68" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="Y68" s="4" t="s">
         <v>361</v>
@@ -8552,18 +8756,21 @@
         <v>3</v>
       </c>
       <c r="AB68" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AD68" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="69" spans="2:30" s="5" customFormat="1">
+    <row r="69" spans="1:30" s="5" customFormat="1">
+      <c r="A69" s="5">
+        <v>68</v>
+      </c>
       <c r="B69" s="6" t="s">
         <v>107</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E69" s="10">
         <v>910</v>
@@ -8581,7 +8788,7 @@
         <v>23</v>
       </c>
       <c r="S69" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T69" s="6" t="s">
         <v>250</v>
@@ -8593,7 +8800,7 @@
         <v>354</v>
       </c>
       <c r="W69" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Y69" s="4" t="s">
         <v>361</v>
@@ -8605,12 +8812,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="70" spans="2:30" s="5" customFormat="1">
+    <row r="70" spans="1:30" s="5" customFormat="1">
+      <c r="A70" s="5">
+        <v>69</v>
+      </c>
       <c r="B70" s="6" t="s">
         <v>109</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E70" s="10">
         <v>1260</v>
@@ -8628,7 +8838,7 @@
         <v>23</v>
       </c>
       <c r="S70" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="T70" s="6" t="s">
         <v>251</v>
@@ -8640,7 +8850,7 @@
         <v>354</v>
       </c>
       <c r="W70" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Y70" s="4" t="s">
         <v>361</v>
@@ -8649,18 +8859,21 @@
         <v>3</v>
       </c>
       <c r="AB70" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AD70" s="6" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="71" spans="2:30" s="5" customFormat="1">
+    <row r="71" spans="1:30" s="5" customFormat="1">
+      <c r="A71" s="5">
+        <v>70</v>
+      </c>
       <c r="B71" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E71" s="10">
         <v>5150</v>
@@ -8685,10 +8898,10 @@
         <v>23</v>
       </c>
       <c r="S71" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="T71" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="U71" s="5" t="s">
         <v>25</v>
@@ -8697,10 +8910,10 @@
         <v>354</v>
       </c>
       <c r="W71" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X71" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Y71" s="4" t="s">
         <v>361</v>
@@ -8712,12 +8925,15 @@
         <v>305</v>
       </c>
     </row>
-    <row r="72" spans="2:30" s="5" customFormat="1">
+    <row r="72" spans="1:30" s="5" customFormat="1">
+      <c r="A72" s="5">
+        <v>71</v>
+      </c>
       <c r="B72" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E72" s="10">
         <v>4950</v>
@@ -8742,10 +8958,10 @@
         <v>23</v>
       </c>
       <c r="S72" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="T72" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="U72" s="5" t="s">
         <v>25</v>
@@ -8754,10 +8970,10 @@
         <v>354</v>
       </c>
       <c r="W72" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X72" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Y72" s="4" t="s">
         <v>361</v>
@@ -8769,12 +8985,15 @@
         <v>305</v>
       </c>
     </row>
-    <row r="73" spans="2:30" s="5" customFormat="1">
+    <row r="73" spans="1:30" s="5" customFormat="1">
+      <c r="A73" s="5">
+        <v>72</v>
+      </c>
       <c r="B73" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E73" s="10">
         <v>4750</v>
@@ -8799,10 +9018,10 @@
         <v>23</v>
       </c>
       <c r="S73" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="T73" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="U73" s="5" t="s">
         <v>25</v>
@@ -8811,10 +9030,10 @@
         <v>354</v>
       </c>
       <c r="W73" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X73" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Y73" s="4" t="s">
         <v>361</v>
@@ -8826,12 +9045,15 @@
         <v>305</v>
       </c>
     </row>
-    <row r="74" spans="2:30" s="5" customFormat="1">
+    <row r="74" spans="1:30" s="5" customFormat="1">
+      <c r="A74" s="5">
+        <v>73</v>
+      </c>
       <c r="B74" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E74" s="10">
         <v>3650</v>
@@ -8855,7 +9077,7 @@
         <v>23</v>
       </c>
       <c r="S74" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="T74" s="6" t="s">
         <v>252</v>
@@ -8867,10 +9089,10 @@
         <v>354</v>
       </c>
       <c r="W74" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="X74" s="7" t="s">
         <v>566</v>
-      </c>
-      <c r="X74" s="7" t="s">
-        <v>567</v>
       </c>
       <c r="Y74" s="4" t="s">
         <v>361</v>
@@ -8882,12 +9104,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="75" spans="2:30" s="5" customFormat="1">
+    <row r="75" spans="1:30" s="5" customFormat="1">
+      <c r="A75" s="5">
+        <v>74</v>
+      </c>
       <c r="B75" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E75" s="10">
         <v>3590</v>
@@ -8911,7 +9136,7 @@
         <v>23</v>
       </c>
       <c r="S75" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="T75" s="6" t="s">
         <v>252</v>
@@ -8923,10 +9148,10 @@
         <v>354</v>
       </c>
       <c r="W75" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="X75" s="7" t="s">
         <v>566</v>
-      </c>
-      <c r="X75" s="7" t="s">
-        <v>567</v>
       </c>
       <c r="Y75" s="4" t="s">
         <v>361</v>
@@ -8938,12 +9163,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="2:30" s="5" customFormat="1">
+    <row r="76" spans="1:30" s="5" customFormat="1">
+      <c r="A76" s="5">
+        <v>75</v>
+      </c>
       <c r="B76" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E76" s="10">
         <v>3210</v>
@@ -8967,7 +9195,7 @@
         <v>23</v>
       </c>
       <c r="S76" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="T76" s="6" t="s">
         <v>252</v>
@@ -8979,10 +9207,10 @@
         <v>354</v>
       </c>
       <c r="W76" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="X76" s="7" t="s">
         <v>566</v>
-      </c>
-      <c r="X76" s="7" t="s">
-        <v>567</v>
       </c>
       <c r="Y76" s="4" t="s">
         <v>361</v>
@@ -8994,7 +9222,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="77" spans="2:30" s="5" customFormat="1">
+    <row r="77" spans="1:30" s="5" customFormat="1">
+      <c r="A77" s="5">
+        <v>76</v>
+      </c>
       <c r="B77" s="6" t="s">
         <v>111</v>
       </c>
@@ -9005,7 +9236,7 @@
         <v>2000</v>
       </c>
       <c r="N77" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="O77" s="5">
         <v>1</v>
@@ -9014,7 +9245,7 @@
         <v>23</v>
       </c>
       <c r="S77" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="T77" s="6" t="s">
         <v>253</v>
@@ -9026,7 +9257,7 @@
         <v>354</v>
       </c>
       <c r="W77" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="Y77" s="4" t="s">
         <v>361</v>
@@ -9038,7 +9269,10 @@
         <v>112</v>
       </c>
     </row>
-    <row r="78" spans="2:30" s="5" customFormat="1">
+    <row r="78" spans="1:30" s="5" customFormat="1">
+      <c r="A78" s="5">
+        <v>77</v>
+      </c>
       <c r="B78" s="6" t="s">
         <v>113</v>
       </c>
@@ -9049,16 +9283,16 @@
         <v>3000</v>
       </c>
       <c r="N78" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="O78" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="R78" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="S78" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="T78" s="6" t="s">
         <v>254</v>
@@ -9070,7 +9304,7 @@
         <v>354</v>
       </c>
       <c r="W78" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="Y78" s="4" t="s">
         <v>361</v>
@@ -9082,12 +9316,15 @@
         <v>114</v>
       </c>
     </row>
-    <row r="79" spans="2:30" s="5" customFormat="1">
+    <row r="79" spans="1:30" s="5" customFormat="1">
+      <c r="A79" s="5">
+        <v>78</v>
+      </c>
       <c r="B79" s="6" t="s">
         <v>115</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E79" s="10">
         <v>1110</v>
@@ -9096,7 +9333,7 @@
         <v>600</v>
       </c>
       <c r="N79" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="O79" s="5">
         <v>1</v>
@@ -9105,7 +9342,7 @@
         <v>23</v>
       </c>
       <c r="S79" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T79" s="6" t="s">
         <v>255</v>
@@ -9117,7 +9354,7 @@
         <v>354</v>
       </c>
       <c r="W79" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="Y79" s="4" t="s">
         <v>361</v>
@@ -9126,18 +9363,21 @@
         <v>3</v>
       </c>
       <c r="AB79" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AD79" s="6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="80" spans="2:30" s="5" customFormat="1">
+    <row r="80" spans="1:30" s="5" customFormat="1">
+      <c r="A80" s="5">
+        <v>79</v>
+      </c>
       <c r="B80" s="6" t="s">
         <v>117</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E80" s="10">
         <v>2520</v>
@@ -9155,10 +9395,10 @@
         <v>23</v>
       </c>
       <c r="S80" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="T80" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="U80" s="5" t="s">
         <v>25</v>
@@ -9167,10 +9407,10 @@
         <v>354</v>
       </c>
       <c r="W80" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="X80" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="Y80" s="4" t="s">
         <v>361</v>
@@ -9179,18 +9419,21 @@
         <v>3</v>
       </c>
       <c r="AB80" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AD80" s="6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="81" spans="2:30" s="5" customFormat="1">
+    <row r="81" spans="1:30" s="5" customFormat="1">
+      <c r="A81" s="5">
+        <v>80</v>
+      </c>
       <c r="B81" s="6" t="s">
         <v>117</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E81" s="10">
         <v>1560</v>
@@ -9208,10 +9451,10 @@
         <v>23</v>
       </c>
       <c r="S81" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="T81" s="6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="U81" s="5" t="s">
         <v>25</v>
@@ -9220,10 +9463,10 @@
         <v>354</v>
       </c>
       <c r="W81" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="X81" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="Y81" s="4" t="s">
         <v>361</v>
@@ -9232,18 +9475,21 @@
         <v>3</v>
       </c>
       <c r="AB81" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AD81" s="6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="82" spans="2:30" s="5" customFormat="1">
+    <row r="82" spans="1:30" s="5" customFormat="1">
+      <c r="A82" s="5">
+        <v>81</v>
+      </c>
       <c r="B82" s="6" t="s">
         <v>119</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E82" s="10">
         <v>1640</v>
@@ -9261,7 +9507,7 @@
         <v>23</v>
       </c>
       <c r="S82" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="T82" s="6" t="s">
         <v>256</v>
@@ -9273,10 +9519,10 @@
         <v>354</v>
       </c>
       <c r="W82" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="X82" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="Y82" s="4" t="s">
         <v>361</v>
@@ -9285,13 +9531,16 @@
         <v>3</v>
       </c>
       <c r="AB82" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AD82" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="83" spans="2:30" s="5" customFormat="1">
+    <row r="83" spans="1:30" s="5" customFormat="1">
+      <c r="A83" s="5">
+        <v>82</v>
+      </c>
       <c r="B83" s="6" t="s">
         <v>121</v>
       </c>
@@ -9314,7 +9563,7 @@
         <v>23</v>
       </c>
       <c r="S83" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T83" s="6" t="s">
         <v>257</v>
@@ -9326,7 +9575,7 @@
         <v>354</v>
       </c>
       <c r="W83" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="Y83" s="4" t="s">
         <v>361</v>
@@ -9338,7 +9587,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="2:30" s="5" customFormat="1">
+    <row r="84" spans="1:30" s="5" customFormat="1">
+      <c r="A84" s="5">
+        <v>83</v>
+      </c>
       <c r="B84" s="6" t="s">
         <v>122</v>
       </c>
@@ -9361,7 +9613,7 @@
         <v>23</v>
       </c>
       <c r="S84" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T84" s="6" t="s">
         <v>258</v>
@@ -9373,10 +9625,10 @@
         <v>354</v>
       </c>
       <c r="W84" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="X84" s="7" t="s">
         <v>587</v>
-      </c>
-      <c r="X84" s="7" t="s">
-        <v>588</v>
       </c>
       <c r="Y84" s="4" t="s">
         <v>361</v>
@@ -9388,12 +9640,15 @@
         <v>297</v>
       </c>
     </row>
-    <row r="85" spans="2:30" s="5" customFormat="1">
+    <row r="85" spans="1:30" s="5" customFormat="1">
+      <c r="A85" s="5">
+        <v>84</v>
+      </c>
       <c r="B85" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E85" s="11">
         <v>5620</v>
@@ -9414,10 +9669,10 @@
         <v>23</v>
       </c>
       <c r="S85" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T85" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="U85" s="5" t="s">
         <v>25</v>
@@ -9426,7 +9681,7 @@
         <v>354</v>
       </c>
       <c r="W85" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Y85" s="4" t="s">
         <v>361</v>
@@ -9438,12 +9693,15 @@
         <v>123</v>
       </c>
     </row>
-    <row r="86" spans="2:30" s="5" customFormat="1">
+    <row r="86" spans="1:30" s="5" customFormat="1">
+      <c r="A86" s="5">
+        <v>85</v>
+      </c>
       <c r="B86" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E86" s="11">
         <v>5470</v>
@@ -9464,10 +9722,10 @@
         <v>23</v>
       </c>
       <c r="S86" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T86" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="U86" s="5" t="s">
         <v>25</v>
@@ -9476,7 +9734,7 @@
         <v>354</v>
       </c>
       <c r="W86" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Y86" s="4" t="s">
         <v>361</v>
@@ -9488,12 +9746,15 @@
         <v>123</v>
       </c>
     </row>
-    <row r="87" spans="2:30" s="5" customFormat="1">
+    <row r="87" spans="1:30" s="5" customFormat="1">
+      <c r="A87" s="5">
+        <v>86</v>
+      </c>
       <c r="B87" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E87" s="11">
         <v>4460</v>
@@ -9514,10 +9775,10 @@
         <v>23</v>
       </c>
       <c r="S87" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T87" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="U87" s="5" t="s">
         <v>25</v>
@@ -9526,7 +9787,7 @@
         <v>354</v>
       </c>
       <c r="W87" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Y87" s="4" t="s">
         <v>361</v>
@@ -9538,7 +9799,10 @@
         <v>123</v>
       </c>
     </row>
-    <row r="88" spans="2:30" s="5" customFormat="1">
+    <row r="88" spans="1:30" s="5" customFormat="1">
+      <c r="A88" s="5">
+        <v>87</v>
+      </c>
       <c r="B88" s="6" t="s">
         <v>124</v>
       </c>
@@ -9561,7 +9825,7 @@
         <v>23</v>
       </c>
       <c r="S88" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T88" s="6" t="s">
         <v>259</v>
@@ -9573,7 +9837,7 @@
         <v>354</v>
       </c>
       <c r="W88" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="Y88" s="4" t="s">
         <v>361</v>
@@ -9585,12 +9849,15 @@
         <v>125</v>
       </c>
     </row>
-    <row r="89" spans="2:30" s="5" customFormat="1">
+    <row r="89" spans="1:30" s="5" customFormat="1">
+      <c r="A89" s="5">
+        <v>88</v>
+      </c>
       <c r="B89" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E89" s="10">
         <v>820</v>
@@ -9608,7 +9875,7 @@
         <v>23</v>
       </c>
       <c r="S89" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="T89" s="6" t="s">
         <v>260</v>
@@ -9617,13 +9884,13 @@
         <v>25</v>
       </c>
       <c r="V89" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="W89" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="X89" s="7" t="s">
         <v>599</v>
-      </c>
-      <c r="X89" s="7" t="s">
-        <v>600</v>
       </c>
       <c r="Y89" s="4" t="s">
         <v>431</v>
@@ -9635,12 +9902,15 @@
         <v>298</v>
       </c>
     </row>
-    <row r="90" spans="2:30" s="5" customFormat="1">
+    <row r="90" spans="1:30" s="5" customFormat="1">
+      <c r="A90" s="5">
+        <v>89</v>
+      </c>
       <c r="B90" s="6" t="s">
         <v>127</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E90" s="10">
         <v>900</v>
@@ -9652,13 +9922,13 @@
         <v>395</v>
       </c>
       <c r="O90" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="R90" s="5" t="s">
         <v>23</v>
       </c>
       <c r="S90" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="T90" s="6" t="s">
         <v>261</v>
@@ -9667,13 +9937,13 @@
         <v>25</v>
       </c>
       <c r="V90" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="W90" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="X90" s="7" t="s">
         <v>599</v>
-      </c>
-      <c r="X90" s="7" t="s">
-        <v>600</v>
       </c>
       <c r="Y90" s="4" t="s">
         <v>431</v>
@@ -9685,12 +9955,15 @@
         <v>128</v>
       </c>
     </row>
-    <row r="91" spans="2:30" s="5" customFormat="1">
+    <row r="91" spans="1:30" s="5" customFormat="1">
+      <c r="A91" s="5">
+        <v>90</v>
+      </c>
       <c r="B91" s="6" t="s">
         <v>129</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E91" s="10">
         <v>1620</v>
@@ -9708,7 +9981,7 @@
         <v>23</v>
       </c>
       <c r="S91" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="T91" s="6" t="s">
         <v>262</v>
@@ -9717,13 +9990,13 @@
         <v>25</v>
       </c>
       <c r="V91" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="W91" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="X91" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Y91" s="4" t="s">
         <v>431</v>
@@ -9735,12 +10008,15 @@
         <v>299</v>
       </c>
     </row>
-    <row r="92" spans="2:30" s="5" customFormat="1">
+    <row r="92" spans="1:30" s="5" customFormat="1">
+      <c r="A92" s="5">
+        <v>91</v>
+      </c>
       <c r="B92" s="6" t="s">
         <v>130</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E92" s="5">
         <v>730</v>
@@ -9758,7 +10034,7 @@
         <v>23</v>
       </c>
       <c r="S92" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="T92" s="6" t="s">
         <v>263</v>
@@ -9770,7 +10046,7 @@
         <v>354</v>
       </c>
       <c r="W92" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="Y92" s="4" t="s">
         <v>431</v>
@@ -9782,12 +10058,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="93" spans="2:30" s="5" customFormat="1">
+    <row r="93" spans="1:30" s="5" customFormat="1">
+      <c r="A93" s="5">
+        <v>92</v>
+      </c>
       <c r="B93" s="6" t="s">
         <v>132</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E93" s="10">
         <v>1100</v>
@@ -9805,7 +10084,7 @@
         <v>23</v>
       </c>
       <c r="S93" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="T93" s="6" t="s">
         <v>264</v>
@@ -9814,10 +10093,10 @@
         <v>25</v>
       </c>
       <c r="V93" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="W93" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Y93" s="4" t="s">
         <v>431</v>
@@ -9829,12 +10108,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="94" spans="2:30" s="5" customFormat="1">
+    <row r="94" spans="1:30" s="5" customFormat="1">
+      <c r="A94" s="5">
+        <v>93</v>
+      </c>
       <c r="B94" s="6" t="s">
         <v>134</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E94" s="10">
         <v>890</v>
@@ -9852,7 +10134,7 @@
         <v>23</v>
       </c>
       <c r="S94" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="T94" s="6" t="s">
         <v>265</v>
@@ -9864,7 +10146,7 @@
         <v>354</v>
       </c>
       <c r="W94" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Y94" s="4" t="s">
         <v>431</v>
@@ -9876,12 +10158,15 @@
         <v>300</v>
       </c>
     </row>
-    <row r="95" spans="2:30" s="5" customFormat="1">
+    <row r="95" spans="1:30" s="5" customFormat="1">
+      <c r="A95" s="5">
+        <v>94</v>
+      </c>
       <c r="B95" s="6" t="s">
         <v>135</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E95" s="5">
         <v>1000</v>
@@ -9896,10 +10181,10 @@
         <v>23</v>
       </c>
       <c r="S95" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="T95" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="U95" s="5" t="s">
         <v>25</v>
@@ -9908,7 +10193,7 @@
         <v>354</v>
       </c>
       <c r="W95" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="Y95" s="4" t="s">
         <v>431</v>
@@ -9917,18 +10202,21 @@
         <v>3</v>
       </c>
       <c r="AB95" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AD95" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="96" spans="2:30" s="5" customFormat="1">
+    <row r="96" spans="1:30" s="5" customFormat="1">
+      <c r="A96" s="5">
+        <v>95</v>
+      </c>
       <c r="B96" s="16" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E96" s="8">
         <v>740</v>
@@ -9949,19 +10237,19 @@
         <v>387</v>
       </c>
       <c r="T96" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="U96" s="5" t="s">
         <v>25</v>
       </c>
       <c r="V96" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="W96" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="X96" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="Y96" s="4" t="s">
         <v>431</v>
@@ -9970,15 +10258,18 @@
         <v>3</v>
       </c>
       <c r="AD96" s="16" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="97" spans="2:30" s="5" customFormat="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" s="5" customFormat="1">
+      <c r="A97" s="5">
+        <v>96</v>
+      </c>
       <c r="B97" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E97" s="5">
         <v>830</v>
@@ -9999,19 +10290,19 @@
         <v>387</v>
       </c>
       <c r="T97" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="U97" s="5" t="s">
         <v>25</v>
       </c>
       <c r="V97" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="W97" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="X97" s="7" t="s">
         <v>623</v>
-      </c>
-      <c r="X97" s="7" t="s">
-        <v>624</v>
       </c>
       <c r="Y97" s="4" t="s">
         <v>431</v>
@@ -10020,15 +10311,18 @@
         <v>3</v>
       </c>
       <c r="AD97" s="16" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="98" spans="2:30" s="5" customFormat="1">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30" s="5" customFormat="1">
+      <c r="A98" s="5">
+        <v>97</v>
+      </c>
       <c r="B98" s="16" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E98" s="5">
         <v>700</v>
@@ -10049,19 +10343,19 @@
         <v>387</v>
       </c>
       <c r="T98" s="6" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="U98" s="5" t="s">
         <v>25</v>
       </c>
       <c r="V98" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="W98" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="X98" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="Y98" s="4" t="s">
         <v>431</v>
@@ -10070,15 +10364,18 @@
         <v>3</v>
       </c>
       <c r="AD98" s="16" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="99" spans="2:30" s="5" customFormat="1">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30" s="5" customFormat="1">
+      <c r="A99" s="5">
+        <v>98</v>
+      </c>
       <c r="B99" s="16" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E99" s="5">
         <v>750</v>
@@ -10099,19 +10396,19 @@
         <v>387</v>
       </c>
       <c r="T99" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="U99" s="5" t="s">
         <v>25</v>
       </c>
       <c r="V99" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="W99" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="X99" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="Y99" s="4" t="s">
         <v>431</v>
@@ -10120,10 +10417,13 @@
         <v>3</v>
       </c>
       <c r="AD99" s="16" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="100" spans="2:30" s="5" customFormat="1">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30" s="5" customFormat="1">
+      <c r="A100" s="5">
+        <v>99</v>
+      </c>
       <c r="B100" s="6" t="s">
         <v>147</v>
       </c>
@@ -10155,13 +10455,13 @@
         <v>25</v>
       </c>
       <c r="V100" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="W100" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="X100" s="7" t="s">
         <v>637</v>
-      </c>
-      <c r="X100" s="7" t="s">
-        <v>638</v>
       </c>
       <c r="Y100" s="4" t="s">
         <v>431</v>
@@ -10173,12 +10473,15 @@
         <v>301</v>
       </c>
     </row>
-    <row r="101" spans="2:30" s="5" customFormat="1">
+    <row r="101" spans="1:30" s="5" customFormat="1">
+      <c r="A101" s="5">
+        <v>100</v>
+      </c>
       <c r="B101" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E101" s="10">
         <v>680</v>
@@ -10208,7 +10511,7 @@
         <v>354</v>
       </c>
       <c r="W101" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="Y101" s="4" t="s">
         <v>361</v>
@@ -10220,12 +10523,15 @@
         <v>149</v>
       </c>
     </row>
-    <row r="102" spans="2:30" s="5" customFormat="1">
+    <row r="102" spans="1:30" s="5" customFormat="1">
+      <c r="A102" s="5">
+        <v>101</v>
+      </c>
       <c r="B102" s="6" t="s">
         <v>150</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E102" s="10">
         <v>610</v>
@@ -10243,7 +10549,7 @@
         <v>23</v>
       </c>
       <c r="S102" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="T102" s="6" t="s">
         <v>268</v>
@@ -10252,13 +10558,13 @@
         <v>25</v>
       </c>
       <c r="V102" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="W102" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="X102" s="7" t="s">
         <v>640</v>
-      </c>
-      <c r="X102" s="7" t="s">
-        <v>641</v>
       </c>
       <c r="Y102" s="4" t="s">
         <v>361</v>
@@ -10270,7 +10576,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="103" spans="2:30" s="5" customFormat="1">
+    <row r="103" spans="1:30" s="5" customFormat="1">
+      <c r="A103" s="5">
+        <v>102</v>
+      </c>
       <c r="B103" s="6" t="s">
         <v>151</v>
       </c>
@@ -10296,7 +10605,7 @@
         <v>23</v>
       </c>
       <c r="S103" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="T103" s="6" t="s">
         <v>269</v>
@@ -10308,10 +10617,10 @@
         <v>354</v>
       </c>
       <c r="W103" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="X103" s="7" t="s">
         <v>644</v>
-      </c>
-      <c r="X103" s="7" t="s">
-        <v>645</v>
       </c>
       <c r="Y103" s="4" t="s">
         <v>389</v>
@@ -10323,12 +10632,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="104" spans="2:30" s="5" customFormat="1">
+    <row r="104" spans="1:30" s="5" customFormat="1">
+      <c r="A104" s="5">
+        <v>103</v>
+      </c>
       <c r="B104" s="6" t="s">
         <v>153</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E104" s="10">
         <v>3320</v>
@@ -10343,7 +10655,7 @@
         <v>1970</v>
       </c>
       <c r="N104" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="O104" s="5">
         <v>1</v>
@@ -10352,7 +10664,7 @@
         <v>23</v>
       </c>
       <c r="S104" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="T104" s="6" t="s">
         <v>270</v>
@@ -10364,10 +10676,10 @@
         <v>354</v>
       </c>
       <c r="W104" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="X104" s="7" t="s">
         <v>646</v>
-      </c>
-      <c r="X104" s="7" t="s">
-        <v>647</v>
       </c>
       <c r="Y104" s="4" t="s">
         <v>361</v>
@@ -10379,7 +10691,10 @@
         <v>154</v>
       </c>
     </row>
-    <row r="105" spans="2:30" s="5" customFormat="1">
+    <row r="105" spans="1:30" s="5" customFormat="1">
+      <c r="A105" s="5">
+        <v>104</v>
+      </c>
       <c r="B105" s="6" t="s">
         <v>155</v>
       </c>
@@ -10403,7 +10718,7 @@
         <v>23</v>
       </c>
       <c r="S105" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="T105" s="6" t="s">
         <v>271</v>
@@ -10412,10 +10727,10 @@
         <v>25</v>
       </c>
       <c r="V105" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="W105" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="Y105" s="4" t="s">
         <v>361</v>
@@ -10424,18 +10739,21 @@
         <v>3</v>
       </c>
       <c r="AB105" s="5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AD105" s="6" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="106" spans="2:30" s="5" customFormat="1">
+    <row r="106" spans="1:30" s="5" customFormat="1">
+      <c r="A106" s="5">
+        <v>105</v>
+      </c>
       <c r="B106" s="6" t="s">
         <v>157</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E106" s="10">
         <v>6000</v>
@@ -10456,7 +10774,7 @@
         <v>23</v>
       </c>
       <c r="S106" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="T106" s="6" t="s">
         <v>272</v>
@@ -10465,13 +10783,13 @@
         <v>25</v>
       </c>
       <c r="V106" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="W106" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="X106" s="7" t="s">
         <v>653</v>
-      </c>
-      <c r="X106" s="7" t="s">
-        <v>654</v>
       </c>
       <c r="Y106" s="4" t="s">
         <v>361</v>
@@ -10480,18 +10798,21 @@
         <v>5</v>
       </c>
       <c r="AB106" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AD106" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="107" spans="2:30" s="5" customFormat="1">
+    <row r="107" spans="1:30" s="5" customFormat="1">
+      <c r="A107" s="5">
+        <v>106</v>
+      </c>
       <c r="B107" s="6" t="s">
         <v>157</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E107" s="10">
         <v>6400</v>
@@ -10512,7 +10833,7 @@
         <v>23</v>
       </c>
       <c r="S107" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="T107" s="6" t="s">
         <v>272</v>
@@ -10521,13 +10842,13 @@
         <v>25</v>
       </c>
       <c r="V107" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="W107" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="X107" s="7" t="s">
         <v>653</v>
-      </c>
-      <c r="X107" s="7" t="s">
-        <v>654</v>
       </c>
       <c r="Y107" s="4" t="s">
         <v>361</v>
@@ -10536,18 +10857,21 @@
         <v>3</v>
       </c>
       <c r="AB107" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AD107" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="108" spans="2:30" s="5" customFormat="1">
+    <row r="108" spans="1:30" s="5" customFormat="1">
+      <c r="A108" s="5">
+        <v>107</v>
+      </c>
       <c r="B108" s="6" t="s">
         <v>159</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E108" s="10">
         <v>5000</v>
@@ -10568,7 +10892,7 @@
         <v>23</v>
       </c>
       <c r="S108" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="T108" s="6" t="s">
         <v>273</v>
@@ -10577,13 +10901,13 @@
         <v>25</v>
       </c>
       <c r="V108" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="W108" s="7" t="s">
         <v>659</v>
       </c>
-      <c r="W108" s="7" t="s">
+      <c r="X108" s="7" t="s">
         <v>660</v>
-      </c>
-      <c r="X108" s="7" t="s">
-        <v>661</v>
       </c>
       <c r="Y108" s="4" t="s">
         <v>361</v>
@@ -10595,12 +10919,15 @@
         <v>160</v>
       </c>
     </row>
-    <row r="109" spans="2:30" s="5" customFormat="1">
+    <row r="109" spans="1:30" s="5" customFormat="1">
+      <c r="A109" s="5">
+        <v>108</v>
+      </c>
       <c r="B109" s="6" t="s">
         <v>161</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E109" s="10">
         <v>1580</v>
@@ -10621,7 +10948,7 @@
         <v>23</v>
       </c>
       <c r="S109" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="T109" s="6" t="s">
         <v>274</v>
@@ -10633,10 +10960,10 @@
         <v>354</v>
       </c>
       <c r="W109" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="X109" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="Y109" s="4" t="s">
         <v>361</v>
@@ -10648,12 +10975,15 @@
         <v>162</v>
       </c>
     </row>
-    <row r="110" spans="2:30" s="5" customFormat="1">
+    <row r="110" spans="1:30" s="5" customFormat="1">
+      <c r="A110" s="5">
+        <v>109</v>
+      </c>
       <c r="B110" s="6" t="s">
         <v>163</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E110" s="10">
         <v>620</v>
@@ -10674,7 +11004,7 @@
         <v>23</v>
       </c>
       <c r="S110" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="T110" s="6" t="s">
         <v>275</v>
@@ -10686,10 +11016,10 @@
         <v>354</v>
       </c>
       <c r="W110" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="X110" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Y110" s="4" t="s">
         <v>361</v>
@@ -10701,12 +11031,15 @@
         <v>164</v>
       </c>
     </row>
-    <row r="111" spans="2:30" s="5" customFormat="1" ht="19">
+    <row r="111" spans="1:30" s="5" customFormat="1" ht="19">
+      <c r="A111" s="5">
+        <v>110</v>
+      </c>
       <c r="B111" s="21" t="s">
-        <v>687</v>
-      </c>
-      <c r="C111" s="21" t="s">
-        <v>707</v>
+        <v>686</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>706</v>
       </c>
       <c r="E111" s="5">
         <v>15000</v>
@@ -10727,22 +11060,22 @@
         <v>23</v>
       </c>
       <c r="S111" s="5" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="T111" s="22" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="U111" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="V111" s="6" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="W111" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="X111" s="7" t="s">
         <v>722</v>
-      </c>
-      <c r="X111" s="7" t="s">
-        <v>723</v>
       </c>
       <c r="Y111" s="20" t="s">
         <v>361</v>
@@ -10750,16 +11083,22 @@
       <c r="Z111" s="5">
         <v>5</v>
       </c>
+      <c r="AB111" s="5" t="s">
+        <v>735</v>
+      </c>
       <c r="AD111" s="19" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="112" spans="2:30" s="5" customFormat="1" ht="19">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="112" spans="1:30" s="5" customFormat="1" ht="19">
+      <c r="A112" s="5">
+        <v>111</v>
+      </c>
       <c r="B112" s="21" t="s">
-        <v>688</v>
-      </c>
-      <c r="C112" s="23" t="s">
-        <v>708</v>
+        <v>687</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>707</v>
       </c>
       <c r="E112" s="5">
         <v>6500</v>
@@ -10771,7 +11110,7 @@
       <c r="L112" s="9"/>
       <c r="M112" s="9"/>
       <c r="N112" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="O112" s="5">
         <v>5</v>
@@ -10780,22 +11119,22 @@
         <v>23</v>
       </c>
       <c r="S112" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="T112" s="22" t="s">
+        <v>693</v>
+      </c>
+      <c r="U112" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="V112" s="6" t="s">
         <v>713</v>
       </c>
-      <c r="T112" s="22" t="s">
-        <v>694</v>
-      </c>
-      <c r="U112" s="4" t="s">
-        <v>698</v>
-      </c>
-      <c r="V112" s="6" t="s">
+      <c r="W112" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="W112" s="7" t="s">
+      <c r="X112" s="7" t="s">
         <v>715</v>
-      </c>
-      <c r="X112" s="7" t="s">
-        <v>716</v>
       </c>
       <c r="Y112" s="20" t="s">
         <v>361</v>
@@ -10804,15 +11143,18 @@
         <v>5</v>
       </c>
       <c r="AD112" s="19" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="113" spans="2:30" s="5" customFormat="1" ht="16">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="113" spans="1:30" s="5" customFormat="1" ht="16">
+      <c r="A113" s="5">
+        <v>112</v>
+      </c>
       <c r="B113" s="21" t="s">
-        <v>689</v>
-      </c>
-      <c r="C113" s="23" t="s">
-        <v>731</v>
+        <v>688</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>730</v>
       </c>
       <c r="E113" s="5">
         <v>8000</v>
@@ -10824,7 +11166,7 @@
       <c r="L113" s="9"/>
       <c r="M113" s="9"/>
       <c r="N113" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="O113" s="5">
         <v>4</v>
@@ -10836,19 +11178,19 @@
         <v>397</v>
       </c>
       <c r="T113" s="22" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="U113" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="V113" s="6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="W113" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="X113" s="7" t="s">
         <v>726</v>
-      </c>
-      <c r="X113" s="7" t="s">
-        <v>727</v>
       </c>
       <c r="Y113" s="20" t="s">
         <v>361</v>
@@ -10857,18 +11199,21 @@
         <v>3</v>
       </c>
       <c r="AB113" s="5" t="s">
-        <v>481</v>
+        <v>734</v>
       </c>
       <c r="AD113" s="19" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="114" spans="2:30" s="5" customFormat="1" ht="19">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="114" spans="1:30" s="5" customFormat="1" ht="19">
+      <c r="A114" s="5">
+        <v>113</v>
+      </c>
       <c r="B114" s="21" t="s">
+        <v>728</v>
+      </c>
+      <c r="C114" s="6" t="s">
         <v>729</v>
-      </c>
-      <c r="C114" s="23" t="s">
-        <v>730</v>
       </c>
       <c r="E114" s="5">
         <v>3000</v>
@@ -10880,7 +11225,7 @@
       <c r="L114" s="9"/>
       <c r="M114" s="9"/>
       <c r="N114" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="O114" s="5">
         <v>2</v>
@@ -10892,19 +11237,19 @@
         <v>397</v>
       </c>
       <c r="T114" s="22" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="U114" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="V114" s="6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="W114" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="X114" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="Y114" s="20" t="s">
         <v>361</v>
@@ -10913,45 +11258,48 @@
         <v>3</v>
       </c>
       <c r="AB114" s="5" t="s">
-        <v>481</v>
+        <v>734</v>
       </c>
       <c r="AD114" s="21" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="115" spans="2:30" s="5" customFormat="1" ht="19">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="115" spans="1:30" s="5" customFormat="1" ht="19">
+      <c r="A115" s="5">
+        <v>114</v>
+      </c>
       <c r="B115" s="21" t="s">
-        <v>690</v>
-      </c>
-      <c r="C115" s="23" t="s">
-        <v>709</v>
+        <v>689</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>708</v>
       </c>
       <c r="K115" s="9"/>
       <c r="L115" s="9"/>
       <c r="M115" s="9"/>
       <c r="N115" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="O115" s="5" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="R115" s="5" t="s">
         <v>23</v>
       </c>
       <c r="S115" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="T115" s="22" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="U115" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="V115" s="6" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="W115" s="7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="Y115" s="4" t="s">
         <v>431</v>
@@ -10960,18 +11308,21 @@
         <v>5</v>
       </c>
       <c r="AB115" s="5" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AD115" s="19" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="116" spans="2:30" s="5" customFormat="1" ht="16">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="116" spans="1:30" s="5" customFormat="1" ht="16">
+      <c r="A116" s="5">
+        <v>115</v>
+      </c>
       <c r="B116" s="21" t="s">
-        <v>692</v>
-      </c>
-      <c r="C116" s="23" t="s">
-        <v>710</v>
+        <v>691</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>709</v>
       </c>
       <c r="E116" s="5">
         <v>1000</v>
@@ -10989,19 +11340,19 @@
         <v>23</v>
       </c>
       <c r="S116" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T116" s="22" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="U116" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="V116" s="6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="W116" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="Y116" s="20" t="s">
         <v>361</v>
@@ -11010,18 +11361,21 @@
         <v>5</v>
       </c>
       <c r="AB116" s="5" t="s">
-        <v>481</v>
+        <v>734</v>
       </c>
       <c r="AD116" s="19" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="117" spans="2:30" s="5" customFormat="1" ht="16">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="117" spans="1:30" s="5" customFormat="1" ht="16">
+      <c r="A117" s="5">
+        <v>116</v>
+      </c>
       <c r="B117" s="5" t="s">
-        <v>691</v>
-      </c>
-      <c r="C117" s="23" t="s">
-        <v>711</v>
+        <v>690</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>710</v>
       </c>
       <c r="E117" s="5">
         <v>2000</v>
@@ -11039,19 +11393,19 @@
         <v>23</v>
       </c>
       <c r="S117" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="T117" s="22" t="s">
+        <v>696</v>
+      </c>
+      <c r="U117" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="U117" s="4" t="s">
-        <v>698</v>
-      </c>
       <c r="V117" s="6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="W117" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="Y117" s="20" t="s">
         <v>361</v>
@@ -11060,13 +11414,13 @@
         <v>5</v>
       </c>
       <c r="AB117" s="5" t="s">
-        <v>481</v>
+        <v>734</v>
       </c>
       <c r="AD117" s="19" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="118" spans="2:30">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="118" spans="1:30">
       <c r="D118" s="17"/>
       <c r="E118" s="17"/>
       <c r="F118" s="17"/>
@@ -11080,7 +11434,7 @@
       <c r="V118" s="2"/>
       <c r="W118" s="2"/>
     </row>
-    <row r="119" spans="2:30">
+    <row r="119" spans="1:30">
       <c r="D119" s="13"/>
       <c r="E119" s="13"/>
       <c r="F119" s="12"/>
@@ -11093,7 +11447,7 @@
       <c r="V119" s="2"/>
       <c r="W119" s="2"/>
     </row>
-    <row r="120" spans="2:30">
+    <row r="120" spans="1:30">
       <c r="D120" s="13"/>
       <c r="E120" s="13"/>
       <c r="F120" s="12"/>
@@ -11103,7 +11457,7 @@
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" spans="2:30">
+    <row r="121" spans="1:30">
       <c r="D121" s="13"/>
       <c r="E121" s="13"/>
       <c r="F121" s="12"/>
@@ -11113,7 +11467,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" spans="2:30">
+    <row r="122" spans="1:30">
       <c r="D122" s="13"/>
       <c r="E122" s="13"/>
       <c r="F122" s="12"/>
@@ -11123,7 +11477,7 @@
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="2:30">
+    <row r="123" spans="1:30">
       <c r="D123" s="13"/>
       <c r="E123" s="13"/>
       <c r="F123" s="12"/>
@@ -11133,7 +11487,7 @@
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="2:30">
+    <row r="124" spans="1:30">
       <c r="D124" s="13"/>
       <c r="E124" s="13"/>
       <c r="F124" s="12"/>
@@ -11143,7 +11497,7 @@
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="2:30" ht="16">
+    <row r="125" spans="1:30" ht="16">
       <c r="G125" s="18"/>
       <c r="H125" s="18"/>
       <c r="I125" s="18"/>
@@ -11152,7 +11506,7 @@
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="2:30" ht="16">
+    <row r="126" spans="1:30" ht="16">
       <c r="G126" s="19"/>
       <c r="H126" s="19"/>
       <c r="I126" s="19"/>
@@ -11161,7 +11515,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="2:30" ht="16">
+    <row r="127" spans="1:30" ht="16">
       <c r="G127" s="19"/>
       <c r="H127" s="19"/>
       <c r="I127" s="19"/>
@@ -11170,7 +11524,7 @@
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="2:30" ht="16">
+    <row r="128" spans="1:30" ht="16">
       <c r="G128" s="19"/>
       <c r="H128" s="19"/>
       <c r="I128" s="19"/>
